--- a/testdata/sample.xlsx
+++ b/testdata/sample.xlsx
@@ -459,7 +459,7 @@
         <v>1000001</v>
       </c>
       <c r="E3" t="str">
-        <v>¥8,500</v>
+        <v>￥8,500</v>
       </c>
       <c r="F3" t="str">
         <v>2026-01-20</v>

--- a/testdata/sample.xlsx
+++ b/testdata/sample.xlsx
@@ -424,7 +424,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>株式会社ヤマト商事</v>
+        <v>株式会社甲野商事</v>
       </c>
       <c r="B2" t="str">
         <v>田中 一郎</v>
@@ -447,7 +447,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>(株)ヤマト商事</v>
+        <v>(株)甲野商事</v>
       </c>
       <c r="B3" t="str">
         <v xml:space="preserve">佐藤 花子 </v>
@@ -470,7 +470,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>㈱ヤマト商事</v>
+        <v>㈱甲野商事</v>
       </c>
       <c r="B4" t="str">
         <v>鈴木　次郎</v>
@@ -493,13 +493,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>さくら物産株式会社</v>
+        <v>乙川物産株式会社</v>
       </c>
       <c r="B5" t="str">
         <v/>
       </c>
       <c r="C5" t="str">
-        <v>06-9876-5432</v>
+        <v>06-1234-5678</v>
       </c>
       <c r="D5" t="str">
         <v>530-0001</v>
@@ -516,13 +516,13 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>さくら物産㈱</v>
+        <v>乙川物産㈱</v>
       </c>
       <c r="B6" t="str">
         <v>高橋 三郎</v>
       </c>
       <c r="C6" t="str">
-        <v>０６-９８７６-５４３２</v>
+        <v>０６-１２３４-５６７８</v>
       </c>
       <c r="D6" t="str">
         <v>530-0002</v>
@@ -539,13 +539,13 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>みどり工業</v>
+        <v>丙山工業</v>
       </c>
       <c r="B7" t="str">
         <v>伊藤 四郎</v>
       </c>
       <c r="C7" t="str">
-        <v>045-111-2222</v>
+        <v>045-000-0000</v>
       </c>
       <c r="D7" t="str">
         <v>220-0011</v>
@@ -562,13 +562,13 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v xml:space="preserve">みどり工業 </v>
+        <v xml:space="preserve">丙山工業 </v>
       </c>
       <c r="B8" t="str">
         <v>渡辺 五郎</v>
       </c>
       <c r="C8" t="str">
-        <v>045-111-2222</v>
+        <v>045-000-0000</v>
       </c>
       <c r="D8" t="str">
         <v>220-0011</v>
@@ -585,13 +585,13 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>あおぞら商店</v>
+        <v>丁田商店</v>
       </c>
       <c r="B9" t="str">
         <v>山本 六郎</v>
       </c>
       <c r="C9" t="str">
-        <v>011-333-4444</v>
+        <v>011-000-0000</v>
       </c>
       <c r="D9" t="str">
         <v>060-0001</v>
